--- a/InputData/trans/BVS/BAU Vehicle Subsidy.xlsx
+++ b/InputData/trans/BVS/BAU Vehicle Subsidy.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28712"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/skorpius/My Drive/2024/FO local_EPS ICM/Diario/20250317_Trans2/BVS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\Mexico EPS\InputData\trans\BVS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="149" documentId="13_ncr:1_{CA2D9201-8E71-0842-AA9C-A4DF09A0B696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F5DF023-4F49-40CB-A578-39AAD5FB9994}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2F8491-A6C3-4729-90EA-69570E7AC904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="27760" windowHeight="18760" firstSheet="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33465" yWindow="900" windowWidth="22785" windowHeight="14115" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="BVS-psgr-LDVs" sheetId="2" r:id="rId4"/>
     <sheet name="BVS-psgr-HDVs" sheetId="101" r:id="rId5"/>
     <sheet name="BVS-psgr-aircraft" sheetId="105" r:id="rId6"/>
-    <sheet name="BVP-psgr-rail" sheetId="104" r:id="rId7"/>
+    <sheet name="BVS-psgr-rail" sheetId="104" r:id="rId7"/>
     <sheet name="BVS-psgr-ships" sheetId="103" r:id="rId8"/>
     <sheet name="BVS-psgr-motorbikes" sheetId="102" r:id="rId9"/>
     <sheet name="frgt" sheetId="106" r:id="rId10"/>
@@ -276,7 +276,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -840,17 +840,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B37"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="69.28515625" customWidth="1"/>
+    <col min="2" max="2" width="69.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -858,27 +858,27 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" s="3">
         <v>2024</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" s="6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" s="7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>2023</v>
       </c>
@@ -886,7 +886,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>2024</v>
       </c>
@@ -894,12 +894,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>2018</v>
       </c>
@@ -907,35 +907,35 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B17" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B18" s="3"/>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>20.125</v>
       </c>
@@ -943,7 +943,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>0.78500000000000003</v>
       </c>
@@ -951,13 +951,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B32" s="3"/>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B34" s="4"/>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
     </row>
   </sheetData>
@@ -979,7 +979,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -991,12 +991,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="15.95">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>56</v>
       </c>
@@ -1151,7 +1151,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>59</v>
       </c>
@@ -1616,7 +1616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>61</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>62</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>63</v>
       </c>
@@ -2248,12 +2248,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="15.95">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>56</v>
       </c>
@@ -2408,7 +2408,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -2563,7 +2563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>59</v>
       </c>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -3028,7 +3028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>61</v>
       </c>
@@ -3183,7 +3183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>62</v>
       </c>
@@ -3338,7 +3338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>63</v>
       </c>
@@ -3504,12 +3504,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="15.95">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>56</v>
       </c>
@@ -3664,7 +3664,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -3819,7 +3819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -3974,7 +3974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>59</v>
       </c>
@@ -4129,7 +4129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -4284,7 +4284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>61</v>
       </c>
@@ -4439,7 +4439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>62</v>
       </c>
@@ -4594,7 +4594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>63</v>
       </c>
@@ -4760,12 +4760,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="15.95">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>56</v>
       </c>
@@ -4920,7 +4920,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -5075,7 +5075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -5230,7 +5230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>59</v>
       </c>
@@ -5385,7 +5385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -5540,7 +5540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>61</v>
       </c>
@@ -5695,7 +5695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>62</v>
       </c>
@@ -5850,7 +5850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>63</v>
       </c>
@@ -6016,12 +6016,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="15.95">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>56</v>
       </c>
@@ -6176,7 +6176,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -6331,7 +6331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -6486,7 +6486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>59</v>
       </c>
@@ -6641,7 +6641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -6796,7 +6796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>61</v>
       </c>
@@ -6951,7 +6951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>62</v>
       </c>
@@ -7106,7 +7106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>63</v>
       </c>
@@ -7272,12 +7272,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="15.95">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>56</v>
       </c>
@@ -7432,7 +7432,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -7587,7 +7587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -7742,7 +7742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>59</v>
       </c>
@@ -7897,7 +7897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -8052,7 +8052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>61</v>
       </c>
@@ -8207,7 +8207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>62</v>
       </c>
@@ -8362,7 +8362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>63</v>
       </c>
@@ -8525,15 +8525,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{950095BC-D79E-4CA5-8C63-79500511C350}">
   <dimension ref="A1:Z46"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="13.140625" customWidth="1"/>
-    <col min="13" max="13" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="13.109375" customWidth="1"/>
+    <col min="13" max="13" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
@@ -8541,17 +8541,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:16">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E7" t="s">
         <v>20</v>
       </c>
@@ -8568,7 +8568,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E8">
         <v>0.01</v>
       </c>
@@ -8591,7 +8591,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E9" s="9">
         <v>313163.32</v>
       </c>
@@ -8618,7 +8618,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E10" s="9">
         <v>375795.92</v>
       </c>
@@ -8646,7 +8646,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E11" s="9">
         <v>438428.77</v>
       </c>
@@ -8663,7 +8663,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="E12" s="9">
         <v>563693.74</v>
       </c>
@@ -8691,105 +8691,105 @@
         <v>920396.53811956849</v>
       </c>
     </row>
-    <row r="14" spans="1:16" hidden="1" outlineLevel="1">
+    <row r="14" spans="1:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:16" hidden="1" outlineLevel="1"/>
-    <row r="16" spans="1:16" hidden="1" outlineLevel="1">
+    <row r="15" spans="1:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="16" spans="1:16" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="2:2" hidden="1" outlineLevel="1"/>
-    <row r="18" spans="2:2" hidden="1" outlineLevel="1">
+    <row r="17" spans="2:2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="2:2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="2:2" hidden="1" outlineLevel="1">
+    <row r="19" spans="2:2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="2:2" hidden="1" outlineLevel="1">
+    <row r="20" spans="2:2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="2:2" hidden="1" outlineLevel="1">
+    <row r="21" spans="2:2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B21" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="2:2" hidden="1" outlineLevel="1">
+    <row r="22" spans="2:2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="2:2" hidden="1" outlineLevel="1">
+    <row r="23" spans="2:2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B23" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="2:2" hidden="1" outlineLevel="1"/>
-    <row r="25" spans="2:2" hidden="1" outlineLevel="1">
+    <row r="24" spans="2:2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="2:2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="2:2" hidden="1" outlineLevel="1"/>
-    <row r="27" spans="2:2" hidden="1" outlineLevel="1">
+    <row r="26" spans="2:2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="2:2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="2:2" hidden="1" outlineLevel="1"/>
-    <row r="29" spans="2:2" hidden="1" outlineLevel="1">
+    <row r="28" spans="2:2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="2:2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="2:2" hidden="1" outlineLevel="1">
+    <row r="30" spans="2:2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="31" spans="2:2" hidden="1" outlineLevel="1"/>
-    <row r="32" spans="2:2" hidden="1" outlineLevel="1">
+    <row r="31" spans="2:2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="2:2" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="2:26" hidden="1" outlineLevel="1"/>
-    <row r="34" spans="2:26" hidden="1" outlineLevel="1">
+    <row r="33" spans="2:26" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3"/>
+    <row r="34" spans="2:26" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="35" spans="2:26" hidden="1" outlineLevel="1">
+    <row r="35" spans="2:26" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="2:26" hidden="1" outlineLevel="1">
+    <row r="36" spans="2:26" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="2:26" hidden="1" outlineLevel="1">
+    <row r="37" spans="2:26" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="2:26" collapsed="1"/>
-    <row r="39" spans="2:26">
+    <row r="38" spans="2:26" collapsed="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.3">
       <c r="L39" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="40" spans="2:26">
+    <row r="40" spans="2:26" x14ac:dyDescent="0.3">
       <c r="L40" s="17" t="s">
         <v>52</v>
       </c>
@@ -8808,7 +8808,7 @@
       <c r="Y40" s="18"/>
       <c r="Z40" s="18"/>
     </row>
-    <row r="41" spans="2:26">
+    <row r="41" spans="2:26" x14ac:dyDescent="0.3">
       <c r="M41">
         <v>2022</v>
       </c>
@@ -8852,7 +8852,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="42" spans="2:26">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.3">
       <c r="L42" t="s">
         <v>25</v>
       </c>
@@ -8899,7 +8899,7 @@
         <v>28558.667792194701</v>
       </c>
     </row>
-    <row r="43" spans="2:26">
+    <row r="43" spans="2:26" x14ac:dyDescent="0.3">
       <c r="L43" s="16" t="s">
         <v>53</v>
       </c>
@@ -8946,7 +8946,7 @@
         <v>4395.3922726884484</v>
       </c>
     </row>
-    <row r="44" spans="2:26">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.3">
       <c r="L44" t="s">
         <v>54</v>
       </c>
@@ -9007,7 +9007,7 @@
         <v>32954.060064883146</v>
       </c>
     </row>
-    <row r="46" spans="2:26">
+    <row r="46" spans="2:26" x14ac:dyDescent="0.3">
       <c r="L46" t="s">
         <v>55</v>
       </c>
@@ -9082,7 +9082,7 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9094,12 +9094,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="15.95">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>56</v>
       </c>
@@ -9254,7 +9254,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -9428,7 +9428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -9583,7 +9583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>59</v>
       </c>
@@ -9738,7 +9738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -9893,7 +9893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>61</v>
       </c>
@@ -10048,7 +10048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>62</v>
       </c>
@@ -10203,7 +10203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>63</v>
       </c>
@@ -10370,12 +10370,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="15.95">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>56</v>
       </c>
@@ -10530,7 +10530,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -10685,7 +10685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -10840,7 +10840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>59</v>
       </c>
@@ -10995,7 +10995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -11150,7 +11150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>61</v>
       </c>
@@ -11305,7 +11305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>62</v>
       </c>
@@ -11460,7 +11460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>63</v>
       </c>
@@ -11626,12 +11626,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="15.95">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>56</v>
       </c>
@@ -11786,7 +11786,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -11941,7 +11941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -12096,7 +12096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>59</v>
       </c>
@@ -12251,7 +12251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -12406,7 +12406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>61</v>
       </c>
@@ -12561,7 +12561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>62</v>
       </c>
@@ -12716,7 +12716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>63</v>
       </c>
@@ -12882,12 +12882,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="15.95">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>56</v>
       </c>
@@ -13042,7 +13042,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -13197,7 +13197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -13352,7 +13352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>59</v>
       </c>
@@ -13507,7 +13507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -13662,7 +13662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>61</v>
       </c>
@@ -13817,7 +13817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>62</v>
       </c>
@@ -13972,7 +13972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>63</v>
       </c>
@@ -14138,12 +14138,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="15.95">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>56</v>
       </c>
@@ -14298,7 +14298,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -14453,7 +14453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -14608,7 +14608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>59</v>
       </c>
@@ -14763,7 +14763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -14918,7 +14918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>61</v>
       </c>
@@ -15073,7 +15073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>62</v>
       </c>
@@ -15228,7 +15228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>63</v>
       </c>
@@ -15394,12 +15394,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AY8"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="25.140625" customWidth="1"/>
+    <col min="1" max="1" width="25.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="15.95">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>56</v>
       </c>
@@ -15554,7 +15554,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="2" spans="1:51">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>57</v>
       </c>
@@ -15709,7 +15709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:51">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -15864,7 +15864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:51">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>59</v>
       </c>
@@ -16019,7 +16019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:51">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>60</v>
       </c>
@@ -16174,7 +16174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:51">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>61</v>
       </c>
@@ -16329,7 +16329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:51">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>62</v>
       </c>
@@ -16484,7 +16484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:51">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>63</v>
       </c>
@@ -16645,21 +16645,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
     <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
@@ -16803,14 +16788,52 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EE12702-2F00-4C34-B62E-BB558095A878}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33F18FE0-B2EF-49A1-850E-5EB591ACC98E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6804E63A-64CC-4BC7-855C-920638B46FF8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6804E63A-64CC-4BC7-855C-920638B46FF8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{33F18FE0-B2EF-49A1-850E-5EB591ACC98E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7EE12702-2F00-4C34-B62E-BB558095A878}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>